--- a/reports/pdf_change_20260723.xlsx
+++ b/reports/pdf_change_20260723.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,306억   ·   현금 27억(0.6%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 3종목  /  매도 1종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,207억   ·   현금 27억(0.6%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>353227560</v>
+        <v>354659080</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-23</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-478991100</v>
+        <v>-480932300</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1733172000</v>
+        <v>1740196000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1889118000</v>
+        <v>1896774000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,742억   ·   현금 14억(0.4%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,697억   ·   현금 14억(0.4%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -787,7 +787,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,467억   ·   현금 44억(1.8%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,423억   ·   현금 44억(1.8%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -811,7 +811,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,226억   ·   현금 24억(1.1%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,183억   ·   현금 24억(1.1%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -835,7 +835,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 -0억(-0.1%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 -0억(-0.1%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -859,7 +859,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 469억   ·   현금 1억(0.1%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 1억(0.1%)      당일 2026-07-23  vs  전영업일 2026-07-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
